--- a/results/master_row_threshold_results.xlsx
+++ b/results/master_row_threshold_results.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\이데아\ML_HDD2\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\COIN\ML_HDD2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2465283A-40EC-4842-BF93-65D417DA8C6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2465283A-40EC-4842-BF93-65D417DA8C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_row_threshold_results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -765,9 +778,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -805,7 +818,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -911,7 +924,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1053,7 +1066,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/results/master_row_threshold_results.xlsx
+++ b/results/master_row_threshold_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\COIN\ML_HDD2\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\이데아\ML_HDD2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2465283A-40EC-4842-BF93-65D417DA8C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFEEF89-6020-45EF-B57F-36D2DF33F8A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,6 @@
     <sheet name="master_row_threshold_results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -759,6 +746,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C158F239-7827-4398-8C04-34D24A94C0F9}" name="표2" displayName="표2" ref="A1:L61" totalsRowShown="0">
   <autoFilter ref="A1:L61" xr:uid="{59785569-C3B6-4769-BEAC-0848E73DB11A}"/>
+  <sortState ref="A2:L61">
+    <sortCondition ref="B1:B61"/>
+  </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{6C99DCA4-7E4F-4594-BCC8-003022FA31AD}" name="Timestamp" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{EB7B5831-9E70-4615-A718-6E526ED0F8CD}" name="Model"/>
@@ -778,9 +768,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -818,7 +808,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -924,7 +914,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1066,7 +1056,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1134,37 +1124,37 @@
         <v>46239</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>42</v>
       </c>
       <c r="E2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F2">
-        <v>7.7299999999999994E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="G2">
-        <v>0.34510000000000002</v>
+        <v>0.42120000000000002</v>
       </c>
       <c r="H2">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="I2">
-        <v>0.55649999999999999</v>
+        <v>0.66669999999999996</v>
       </c>
       <c r="J2">
-        <v>0.61329999999999996</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="K2">
-        <v>3.01</v>
+        <v>5.32</v>
       </c>
       <c r="L2">
-        <v>31.5</v>
+        <v>204.5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -1172,37 +1162,37 @@
         <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>43</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F3">
-        <v>8.1900000000000001E-2</v>
+        <v>8.4400000000000003E-2</v>
       </c>
       <c r="G3">
-        <v>0.34320000000000001</v>
+        <v>0.42459999999999998</v>
       </c>
       <c r="H3">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="I3">
-        <v>0.53659999999999997</v>
+        <v>0.65429999999999999</v>
       </c>
       <c r="J3">
-        <v>0.5867</v>
+        <v>0.65429999999999999</v>
       </c>
       <c r="K3">
-        <v>3.12</v>
+        <v>5.73</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -1210,37 +1200,37 @@
         <v>46239</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>44</v>
       </c>
       <c r="E4">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F4">
-        <v>7.7100000000000002E-2</v>
+        <v>8.2400000000000001E-2</v>
       </c>
       <c r="G4">
-        <v>0.35360000000000003</v>
+        <v>0.37459999999999999</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I4">
-        <v>0.50939999999999996</v>
+        <v>0.67810000000000004</v>
       </c>
       <c r="J4">
-        <v>0.6</v>
+        <v>0.61109999999999998</v>
       </c>
       <c r="K4">
-        <v>3.56</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="L4">
-        <v>34</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1248,37 +1238,37 @@
         <v>46239</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>45</v>
       </c>
       <c r="E5">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F5">
-        <v>7.8799999999999995E-2</v>
+        <v>9.0800000000000006E-2</v>
       </c>
       <c r="G5">
-        <v>0.33350000000000002</v>
+        <v>0.41570000000000001</v>
       </c>
       <c r="H5">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I5">
-        <v>0.54879999999999995</v>
+        <v>0.61619999999999997</v>
       </c>
       <c r="J5">
-        <v>0.6</v>
+        <v>0.70369999999999999</v>
       </c>
       <c r="K5">
-        <v>3.04</v>
+        <v>7.27</v>
       </c>
       <c r="L5">
-        <v>30</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -1286,37 +1276,37 @@
         <v>46239</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>46</v>
       </c>
       <c r="E6">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F6">
-        <v>8.1000000000000003E-2</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="G6">
-        <v>0.32279999999999998</v>
+        <v>0.37609999999999999</v>
       </c>
       <c r="H6">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
       <c r="I6">
-        <v>0.55600000000000005</v>
+        <v>0.64849999999999997</v>
       </c>
       <c r="J6">
-        <v>0.59560000000000002</v>
+        <v>0.66049999999999998</v>
       </c>
       <c r="K6">
-        <v>2.93</v>
+        <v>5.94</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1324,7 +1314,7 @@
         <v>46239</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -1336,25 +1326,25 @@
         <v>0.02</v>
       </c>
       <c r="F7">
-        <v>6.7199999999999996E-2</v>
+        <v>7.1800000000000003E-2</v>
       </c>
       <c r="G7">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H7">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="I7">
-        <v>0.50170000000000003</v>
+        <v>0.40770000000000001</v>
       </c>
       <c r="J7">
-        <v>0.64</v>
+        <v>0.65780000000000005</v>
       </c>
       <c r="K7">
-        <v>3.91</v>
+        <v>5.88</v>
       </c>
       <c r="L7">
-        <v>30.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -1362,7 +1352,7 @@
         <v>46239</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -1374,25 +1364,25 @@
         <v>0.02</v>
       </c>
       <c r="F8">
-        <v>6.9699999999999998E-2</v>
+        <v>7.4300000000000005E-2</v>
       </c>
       <c r="G8">
-        <v>0.3599</v>
+        <v>0.36870000000000003</v>
       </c>
       <c r="H8">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="I8">
-        <v>0.48459999999999998</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="J8">
-        <v>0.63109999999999999</v>
+        <v>0.65329999999999999</v>
       </c>
       <c r="K8">
-        <v>4.13</v>
+        <v>5.91</v>
       </c>
       <c r="L8">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -1400,7 +1390,7 @@
         <v>46239</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -1412,25 +1402,25 @@
         <v>0.02</v>
       </c>
       <c r="F9">
-        <v>6.7400000000000002E-2</v>
+        <v>7.7399999999999997E-2</v>
       </c>
       <c r="G9">
-        <v>0.376</v>
+        <v>0.38779999999999998</v>
       </c>
       <c r="H9">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="I9">
-        <v>0.4864</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="J9">
-        <v>0.63560000000000005</v>
+        <v>0.66220000000000001</v>
       </c>
       <c r="K9">
-        <v>4.13</v>
+        <v>5.96</v>
       </c>
       <c r="L9">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -1438,7 +1428,7 @@
         <v>46239</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -1450,25 +1440,25 @@
         <v>0.02</v>
       </c>
       <c r="F10">
-        <v>6.8699999999999997E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="G10">
-        <v>0.37730000000000002</v>
+        <v>0.36780000000000002</v>
       </c>
       <c r="H10">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="I10">
-        <v>0.46689999999999998</v>
+        <v>0.4269</v>
       </c>
       <c r="J10">
-        <v>0.65780000000000005</v>
+        <v>0.66220000000000001</v>
       </c>
       <c r="K10">
-        <v>4.62</v>
+        <v>5.47</v>
       </c>
       <c r="L10">
-        <v>41.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -1476,7 +1466,7 @@
         <v>46239</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -1488,25 +1478,25 @@
         <v>0.02</v>
       </c>
       <c r="F11">
-        <v>6.4600000000000005E-2</v>
+        <v>6.7299999999999999E-2</v>
       </c>
       <c r="G11">
-        <v>0.36130000000000001</v>
+        <v>0.37190000000000001</v>
       </c>
       <c r="H11">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I11">
-        <v>0.4965</v>
+        <v>0.37909999999999999</v>
       </c>
       <c r="J11">
-        <v>0.63560000000000005</v>
+        <v>0.66220000000000001</v>
       </c>
       <c r="K11">
-        <v>3.97</v>
+        <v>6.67</v>
       </c>
       <c r="L11">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1514,37 +1504,37 @@
         <v>46239</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>42</v>
       </c>
       <c r="E12">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F12">
-        <v>7.5700000000000003E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="G12">
-        <v>0.36599999999999999</v>
+        <v>0.45090000000000002</v>
       </c>
       <c r="H12">
-        <v>0.84</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I12">
-        <v>0.45019999999999999</v>
+        <v>0.39079999999999998</v>
       </c>
       <c r="J12">
-        <v>0.62219999999999998</v>
+        <v>0.65069999999999995</v>
       </c>
       <c r="K12">
-        <v>4.68</v>
+        <v>5.69</v>
       </c>
       <c r="L12">
-        <v>37.5</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1552,37 +1542,37 @@
         <v>46239</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>43</v>
       </c>
       <c r="E13">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F13">
-        <v>6.9500000000000006E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="G13">
-        <v>0.35399999999999998</v>
+        <v>0.43759999999999999</v>
       </c>
       <c r="H13">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="I13">
-        <v>0.39510000000000001</v>
+        <v>0.34420000000000001</v>
       </c>
       <c r="J13">
-        <v>0.64439999999999997</v>
+        <v>0.65549999999999997</v>
       </c>
       <c r="K13">
-        <v>6.07</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>47</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1590,37 +1580,37 @@
         <v>46239</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>44</v>
       </c>
       <c r="E14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F14">
-        <v>6.2799999999999995E-2</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="G14">
-        <v>0.37890000000000001</v>
+        <v>0.44950000000000001</v>
       </c>
       <c r="H14">
-        <v>1.06</v>
+        <v>0.68</v>
       </c>
       <c r="I14">
-        <v>0.39779999999999999</v>
+        <v>0.37290000000000001</v>
       </c>
       <c r="J14">
-        <v>0.64890000000000003</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="K14">
-        <v>6.04</v>
+        <v>6.09</v>
       </c>
       <c r="L14">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -1628,37 +1618,37 @@
         <v>46239</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D15">
         <v>45</v>
       </c>
       <c r="E15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F15">
-        <v>7.0300000000000001E-2</v>
+        <v>5.7200000000000001E-2</v>
       </c>
       <c r="G15">
-        <v>0.38640000000000002</v>
+        <v>0.45529999999999998</v>
       </c>
       <c r="H15">
-        <v>0.96</v>
+        <v>0.64</v>
       </c>
       <c r="I15">
-        <v>0.4103</v>
+        <v>0.40429999999999999</v>
       </c>
       <c r="J15">
-        <v>0.64</v>
+        <v>0.63639999999999997</v>
       </c>
       <c r="K15">
-        <v>5.66</v>
+        <v>5.26</v>
       </c>
       <c r="L15">
-        <v>48.5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1666,37 +1656,37 @@
         <v>46239</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D16">
         <v>46</v>
       </c>
       <c r="E16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F16">
-        <v>6.6299999999999998E-2</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="G16">
-        <v>0.3821</v>
+        <v>0.45090000000000002</v>
       </c>
       <c r="H16">
-        <v>1.01</v>
+        <v>0.73</v>
       </c>
       <c r="I16">
-        <v>0.39889999999999998</v>
+        <v>0.41560000000000002</v>
       </c>
       <c r="J16">
-        <v>0.64890000000000003</v>
+        <v>0.63639999999999997</v>
       </c>
       <c r="K16">
-        <v>6.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="L16">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1704,37 +1694,37 @@
         <v>46239</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>42</v>
       </c>
       <c r="E17">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F17">
-        <v>7.1800000000000003E-2</v>
+        <v>9.0399999999999994E-2</v>
       </c>
       <c r="G17">
-        <v>0.39</v>
+        <v>0.36449999999999999</v>
       </c>
       <c r="H17">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="I17">
-        <v>0.40770000000000001</v>
+        <v>0.61329999999999996</v>
       </c>
       <c r="J17">
-        <v>0.65780000000000005</v>
+        <v>0.68520000000000003</v>
       </c>
       <c r="K17">
-        <v>5.88</v>
+        <v>7.16</v>
       </c>
       <c r="L17">
-        <v>49</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1742,10 +1732,10 @@
         <v>46239</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>43</v>
@@ -1754,25 +1744,25 @@
         <v>0.02</v>
       </c>
       <c r="F18">
-        <v>7.4300000000000005E-2</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G18">
-        <v>0.36870000000000003</v>
+        <v>0.3765</v>
       </c>
       <c r="H18">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="I18">
-        <v>0.40500000000000003</v>
+        <v>0.66469999999999996</v>
       </c>
       <c r="J18">
-        <v>0.65329999999999999</v>
+        <v>0.68520000000000003</v>
       </c>
       <c r="K18">
-        <v>5.91</v>
+        <v>5.73</v>
       </c>
       <c r="L18">
-        <v>44</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1780,37 +1770,37 @@
         <v>46239</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19">
         <v>44</v>
       </c>
       <c r="E19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F19">
-        <v>7.7399999999999997E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="G19">
-        <v>0.38779999999999998</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="H19">
-        <v>0.87</v>
+        <v>0.63</v>
       </c>
       <c r="I19">
-        <v>0.40600000000000003</v>
+        <v>0.62570000000000003</v>
       </c>
       <c r="J19">
-        <v>0.66220000000000001</v>
+        <v>0.69140000000000001</v>
       </c>
       <c r="K19">
-        <v>5.96</v>
+        <v>6.86</v>
       </c>
       <c r="L19">
-        <v>48</v>
+        <v>167.5</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1818,37 +1808,37 @@
         <v>46239</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20">
         <v>45</v>
       </c>
       <c r="E20">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F20">
-        <v>8.2500000000000004E-2</v>
+        <v>0.1061</v>
       </c>
       <c r="G20">
-        <v>0.36780000000000002</v>
+        <v>0.24079999999999999</v>
       </c>
       <c r="H20">
-        <v>0.77</v>
+        <v>0.36</v>
       </c>
       <c r="I20">
-        <v>0.4269</v>
+        <v>0.63160000000000005</v>
       </c>
       <c r="J20">
-        <v>0.66220000000000001</v>
+        <v>0.51849999999999996</v>
       </c>
       <c r="K20">
-        <v>5.47</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="L20">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1856,37 +1846,37 @@
         <v>46239</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21">
         <v>46</v>
       </c>
       <c r="E21">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F21">
-        <v>6.7299999999999999E-2</v>
+        <v>7.0900000000000005E-2</v>
       </c>
       <c r="G21">
-        <v>0.37190000000000001</v>
+        <v>0.4254</v>
       </c>
       <c r="H21">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0.37909999999999999</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="J21">
-        <v>0.66220000000000001</v>
+        <v>0.72840000000000005</v>
       </c>
       <c r="K21">
-        <v>6.67</v>
+        <v>7.98</v>
       </c>
       <c r="L21">
-        <v>48</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1897,34 +1887,34 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>42</v>
       </c>
       <c r="E22">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F22">
-        <v>9.0399999999999994E-2</v>
+        <v>7.7299999999999994E-2</v>
       </c>
       <c r="G22">
-        <v>0.36449999999999999</v>
+        <v>0.34510000000000002</v>
       </c>
       <c r="H22">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="I22">
+        <v>0.55649999999999999</v>
+      </c>
+      <c r="J22">
         <v>0.61329999999999996</v>
       </c>
-      <c r="J22">
-        <v>0.68520000000000003</v>
-      </c>
       <c r="K22">
-        <v>7.16</v>
+        <v>3.01</v>
       </c>
       <c r="L22">
-        <v>168</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1935,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>43</v>
@@ -1944,25 +1934,25 @@
         <v>0.02</v>
       </c>
       <c r="F23">
-        <v>7.9699999999999993E-2</v>
+        <v>8.1900000000000001E-2</v>
       </c>
       <c r="G23">
-        <v>0.3765</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="H23">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="I23">
-        <v>0.66469999999999996</v>
+        <v>0.53659999999999997</v>
       </c>
       <c r="J23">
-        <v>0.68520000000000003</v>
+        <v>0.5867</v>
       </c>
       <c r="K23">
-        <v>5.73</v>
+        <v>3.12</v>
       </c>
       <c r="L23">
-        <v>169</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1973,34 +1963,34 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>44</v>
       </c>
       <c r="E24">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F24">
-        <v>9.4E-2</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="G24">
-        <v>0.36699999999999999</v>
+        <v>0.35360000000000003</v>
       </c>
       <c r="H24">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="I24">
-        <v>0.62570000000000003</v>
+        <v>0.50939999999999996</v>
       </c>
       <c r="J24">
-        <v>0.69140000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="K24">
-        <v>6.86</v>
+        <v>3.56</v>
       </c>
       <c r="L24">
-        <v>167.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -2011,34 +2001,34 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>45</v>
       </c>
       <c r="E25">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F25">
-        <v>0.1061</v>
+        <v>7.8799999999999995E-2</v>
       </c>
       <c r="G25">
-        <v>0.24079999999999999</v>
+        <v>0.33350000000000002</v>
       </c>
       <c r="H25">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I25">
-        <v>0.63160000000000005</v>
+        <v>0.54879999999999995</v>
       </c>
       <c r="J25">
-        <v>0.51849999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="K25">
-        <v>5.0199999999999996</v>
+        <v>3.04</v>
       </c>
       <c r="L25">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -2049,34 +2039,34 @@
         <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>46</v>
       </c>
       <c r="E26">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F26">
-        <v>7.0900000000000005E-2</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="G26">
-        <v>0.4254</v>
+        <v>0.32279999999999998</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0.69</v>
       </c>
       <c r="I26">
-        <v>0.60199999999999998</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="J26">
-        <v>0.72840000000000005</v>
+        <v>0.59560000000000002</v>
       </c>
       <c r="K26">
-        <v>7.98</v>
+        <v>2.93</v>
       </c>
       <c r="L26">
-        <v>220.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -2084,37 +2074,37 @@
         <v>46239</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27">
         <v>42</v>
       </c>
       <c r="E27">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F27">
-        <v>7.9799999999999996E-2</v>
+        <v>0.1517</v>
       </c>
       <c r="G27">
-        <v>0.48649999999999999</v>
+        <v>0.22489999999999999</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.11</v>
       </c>
       <c r="I27">
-        <v>0.58850000000000002</v>
+        <v>0.68910000000000005</v>
       </c>
       <c r="J27">
-        <v>0.75929999999999997</v>
+        <v>0.39229999999999998</v>
       </c>
       <c r="K27">
-        <v>8.8000000000000007</v>
+        <v>0.99</v>
       </c>
       <c r="L27">
-        <v>223</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -2122,37 +2112,37 @@
         <v>46239</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28">
         <v>43</v>
       </c>
       <c r="E28">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F28">
-        <v>7.6499999999999999E-2</v>
+        <v>0.1615</v>
       </c>
       <c r="G28">
-        <v>0.44940000000000002</v>
+        <v>0.25690000000000002</v>
       </c>
       <c r="H28">
-        <v>0.97</v>
+        <v>0.11</v>
       </c>
       <c r="I28">
-        <v>0.60909999999999997</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J28">
-        <v>0.74070000000000003</v>
+        <v>0.46410000000000001</v>
       </c>
       <c r="K28">
-        <v>7.88</v>
+        <v>1.05</v>
       </c>
       <c r="L28">
-        <v>243</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -2160,37 +2150,37 @@
         <v>46239</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29">
         <v>44</v>
       </c>
       <c r="E29">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F29">
-        <v>9.3700000000000006E-2</v>
+        <v>0.1615</v>
       </c>
       <c r="G29">
-        <v>0.39910000000000001</v>
+        <v>0.25359999999999999</v>
       </c>
       <c r="H29">
-        <v>0.69</v>
+        <v>0.11</v>
       </c>
       <c r="I29">
-        <v>0.63129999999999997</v>
+        <v>0.71109999999999995</v>
       </c>
       <c r="J29">
-        <v>0.69750000000000001</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="K29">
-        <v>6.76</v>
+        <v>1.05</v>
       </c>
       <c r="L29">
-        <v>184</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -2198,37 +2188,37 @@
         <v>46239</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30">
         <v>45</v>
       </c>
       <c r="E30">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F30">
-        <v>8.0799999999999997E-2</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="G30">
-        <v>0.45929999999999999</v>
+        <v>0.26069999999999999</v>
       </c>
       <c r="H30">
-        <v>0.93</v>
+        <v>0.11</v>
       </c>
       <c r="I30">
-        <v>0.60099999999999998</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J30">
-        <v>0.73460000000000003</v>
+        <v>0.46410000000000001</v>
       </c>
       <c r="K30">
-        <v>8.09</v>
+        <v>1.05</v>
       </c>
       <c r="L30">
-        <v>229</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -2236,37 +2226,37 @@
         <v>46239</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31">
         <v>46</v>
       </c>
       <c r="E31">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F31">
-        <v>7.7600000000000002E-2</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="G31">
-        <v>0.45700000000000002</v>
+        <v>0.26069999999999999</v>
       </c>
       <c r="H31">
-        <v>0.97</v>
+        <v>0.11</v>
       </c>
       <c r="I31">
-        <v>0.60099999999999998</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J31">
-        <v>0.71599999999999997</v>
+        <v>0.46410000000000001</v>
       </c>
       <c r="K31">
-        <v>7.88</v>
+        <v>1.05</v>
       </c>
       <c r="L31">
-        <v>246</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -2464,37 +2454,37 @@
         <v>46239</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>42</v>
       </c>
       <c r="E37">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F37">
-        <v>9.4100000000000003E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
       <c r="G37">
-        <v>0.42120000000000002</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="H37">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="I37">
-        <v>0.66669999999999996</v>
+        <v>0.45019999999999999</v>
       </c>
       <c r="J37">
-        <v>0.64200000000000002</v>
+        <v>0.62219999999999998</v>
       </c>
       <c r="K37">
-        <v>5.32</v>
+        <v>4.68</v>
       </c>
       <c r="L37">
-        <v>204.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2502,37 +2492,37 @@
         <v>46239</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>43</v>
       </c>
       <c r="E38">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F38">
-        <v>8.4400000000000003E-2</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="G38">
-        <v>0.42459999999999998</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="H38">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="I38">
-        <v>0.65429999999999999</v>
+        <v>0.39510000000000001</v>
       </c>
       <c r="J38">
-        <v>0.65429999999999999</v>
+        <v>0.64439999999999997</v>
       </c>
       <c r="K38">
-        <v>5.73</v>
+        <v>6.07</v>
       </c>
       <c r="L38">
-        <v>222</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2540,37 +2530,37 @@
         <v>46239</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>44</v>
       </c>
       <c r="E39">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F39">
-        <v>8.2400000000000001E-2</v>
+        <v>6.2799999999999995E-2</v>
       </c>
       <c r="G39">
-        <v>0.37459999999999999</v>
+        <v>0.37890000000000001</v>
       </c>
       <c r="H39">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="I39">
-        <v>0.67810000000000004</v>
+        <v>0.39779999999999999</v>
       </c>
       <c r="J39">
-        <v>0.61109999999999998</v>
+        <v>0.64890000000000003</v>
       </c>
       <c r="K39">
-        <v>4.8099999999999996</v>
+        <v>6.04</v>
       </c>
       <c r="L39">
-        <v>186</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2578,37 +2568,37 @@
         <v>46239</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>45</v>
       </c>
       <c r="E40">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F40">
-        <v>9.0800000000000006E-2</v>
+        <v>7.0300000000000001E-2</v>
       </c>
       <c r="G40">
-        <v>0.41570000000000001</v>
+        <v>0.38640000000000002</v>
       </c>
       <c r="H40">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="I40">
-        <v>0.61619999999999997</v>
+        <v>0.4103</v>
       </c>
       <c r="J40">
-        <v>0.70369999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="K40">
-        <v>7.27</v>
+        <v>5.66</v>
       </c>
       <c r="L40">
-        <v>206.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2616,37 +2606,37 @@
         <v>46239</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>46</v>
       </c>
       <c r="E41">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F41">
-        <v>8.2799999999999999E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="G41">
-        <v>0.37609999999999999</v>
+        <v>0.3821</v>
       </c>
       <c r="H41">
-        <v>0.74</v>
+        <v>1.01</v>
       </c>
       <c r="I41">
-        <v>0.64849999999999997</v>
+        <v>0.39889999999999998</v>
       </c>
       <c r="J41">
-        <v>0.66049999999999998</v>
+        <v>0.64890000000000003</v>
       </c>
       <c r="K41">
-        <v>5.94</v>
+        <v>6.02</v>
       </c>
       <c r="L41">
-        <v>173</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2654,7 +2644,7 @@
         <v>46239</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -2666,25 +2656,25 @@
         <v>0.01</v>
       </c>
       <c r="F42">
-        <v>0.1517</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="G42">
-        <v>0.22489999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="H42">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="I42">
-        <v>0.68910000000000005</v>
+        <v>0.42009999999999997</v>
       </c>
       <c r="J42">
-        <v>0.39229999999999998</v>
+        <v>0.6411</v>
       </c>
       <c r="K42">
-        <v>0.99</v>
+        <v>4.96</v>
       </c>
       <c r="L42">
-        <v>65</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2692,7 +2682,7 @@
         <v>46239</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -2704,25 +2694,25 @@
         <v>0.01</v>
       </c>
       <c r="F43">
-        <v>0.1615</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="G43">
-        <v>0.25690000000000002</v>
+        <v>0.44030000000000002</v>
       </c>
       <c r="H43">
-        <v>0.11</v>
+        <v>0.66</v>
       </c>
       <c r="I43">
-        <v>0.71319999999999995</v>
+        <v>0.4042</v>
       </c>
       <c r="J43">
-        <v>0.46410000000000001</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="K43">
-        <v>1.05</v>
+        <v>5.34</v>
       </c>
       <c r="L43">
-        <v>51</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2730,7 +2720,7 @@
         <v>46239</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -2742,25 +2732,25 @@
         <v>0.01</v>
       </c>
       <c r="F44">
-        <v>0.1615</v>
+        <v>5.4300000000000001E-2</v>
       </c>
       <c r="G44">
-        <v>0.25359999999999999</v>
+        <v>0.44390000000000002</v>
       </c>
       <c r="H44">
-        <v>0.11</v>
+        <v>0.66</v>
       </c>
       <c r="I44">
-        <v>0.71109999999999995</v>
+        <v>0.4214</v>
       </c>
       <c r="J44">
-        <v>0.45929999999999999</v>
+        <v>0.6411</v>
       </c>
       <c r="K44">
-        <v>1.05</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="L44">
-        <v>47</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2768,7 +2758,7 @@
         <v>46239</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -2780,25 +2770,25 @@
         <v>0.01</v>
       </c>
       <c r="F45">
-        <v>0.16300000000000001</v>
+        <v>5.5199999999999999E-2</v>
       </c>
       <c r="G45">
-        <v>0.26069999999999999</v>
+        <v>0.46560000000000001</v>
       </c>
       <c r="H45">
-        <v>0.11</v>
+        <v>0.68</v>
       </c>
       <c r="I45">
-        <v>0.71319999999999995</v>
+        <v>0.41589999999999999</v>
       </c>
       <c r="J45">
-        <v>0.46410000000000001</v>
+        <v>0.65069999999999995</v>
       </c>
       <c r="K45">
-        <v>1.05</v>
+        <v>5.12</v>
       </c>
       <c r="L45">
-        <v>51</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2806,7 +2796,7 @@
         <v>46239</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -2818,25 +2808,25 @@
         <v>0.01</v>
       </c>
       <c r="F46">
-        <v>0.16300000000000001</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="G46">
-        <v>0.26069999999999999</v>
+        <v>0.44619999999999999</v>
       </c>
       <c r="H46">
-        <v>0.11</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I46">
-        <v>0.71319999999999995</v>
+        <v>0.40410000000000001</v>
       </c>
       <c r="J46">
-        <v>0.46410000000000001</v>
+        <v>0.65549999999999997</v>
       </c>
       <c r="K46">
-        <v>1.05</v>
+        <v>5.42</v>
       </c>
       <c r="L46">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2847,34 +2837,34 @@
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D47">
         <v>42</v>
       </c>
       <c r="E47">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F47">
-        <v>6.3500000000000001E-2</v>
+        <v>7.9799999999999996E-2</v>
       </c>
       <c r="G47">
-        <v>0.39450000000000002</v>
+        <v>0.48649999999999999</v>
       </c>
       <c r="H47">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0.50719999999999998</v>
+        <v>0.58850000000000002</v>
       </c>
       <c r="J47">
-        <v>0.66990000000000005</v>
+        <v>0.75929999999999997</v>
       </c>
       <c r="K47">
-        <v>3.65</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="L47">
-        <v>71</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2885,34 +2875,34 @@
         <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48">
         <v>43</v>
       </c>
       <c r="E48">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F48">
-        <v>6.5500000000000003E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="G48">
-        <v>0.38440000000000002</v>
+        <v>0.44940000000000002</v>
       </c>
       <c r="H48">
-        <v>0.47</v>
+        <v>0.97</v>
       </c>
       <c r="I48">
-        <v>0.53959999999999997</v>
+        <v>0.60909999999999997</v>
       </c>
       <c r="J48">
-        <v>0.68420000000000003</v>
+        <v>0.74070000000000003</v>
       </c>
       <c r="K48">
-        <v>3.27</v>
+        <v>7.88</v>
       </c>
       <c r="L48">
-        <v>67</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2923,34 +2913,34 @@
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49">
         <v>44</v>
       </c>
       <c r="E49">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F49">
-        <v>6.5699999999999995E-2</v>
+        <v>9.3700000000000006E-2</v>
       </c>
       <c r="G49">
-        <v>0.38150000000000001</v>
+        <v>0.39910000000000001</v>
       </c>
       <c r="H49">
-        <v>0.46</v>
+        <v>0.69</v>
       </c>
       <c r="I49">
-        <v>0.50180000000000002</v>
+        <v>0.63129999999999997</v>
       </c>
       <c r="J49">
-        <v>0.66990000000000005</v>
+        <v>0.69750000000000001</v>
       </c>
       <c r="K49">
-        <v>3.73</v>
+        <v>6.76</v>
       </c>
       <c r="L49">
-        <v>72.5</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2961,34 +2951,34 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50">
         <v>45</v>
       </c>
       <c r="E50">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F50">
-        <v>6.4500000000000002E-2</v>
+        <v>8.0799999999999997E-2</v>
       </c>
       <c r="G50">
-        <v>0.37419999999999998</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="H50">
-        <v>0.46</v>
+        <v>0.93</v>
       </c>
       <c r="I50">
-        <v>0.52510000000000001</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="J50">
-        <v>0.65069999999999995</v>
+        <v>0.73460000000000003</v>
       </c>
       <c r="K50">
-        <v>3.3</v>
+        <v>8.09</v>
       </c>
       <c r="L50">
-        <v>61.5</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2999,34 +2989,34 @@
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51">
         <v>46</v>
       </c>
       <c r="E51">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F51">
-        <v>6.9000000000000006E-2</v>
+        <v>7.7600000000000002E-2</v>
       </c>
       <c r="G51">
-        <v>0.34489999999999998</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="H51">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="I51">
-        <v>0.52939999999999998</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="J51">
-        <v>0.64590000000000003</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="K51">
-        <v>3.22</v>
+        <v>7.88</v>
       </c>
       <c r="L51">
-        <v>65</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -3034,37 +3024,37 @@
         <v>46239</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>42</v>
       </c>
       <c r="E52">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F52">
-        <v>5.5800000000000002E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="G52">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="H52">
+        <v>0.94</v>
+      </c>
+      <c r="I52">
+        <v>0.50170000000000003</v>
+      </c>
+      <c r="J52">
         <v>0.64</v>
       </c>
-      <c r="I52">
-        <v>0.42009999999999997</v>
-      </c>
-      <c r="J52">
-        <v>0.6411</v>
-      </c>
       <c r="K52">
-        <v>4.96</v>
+        <v>3.91</v>
       </c>
       <c r="L52">
-        <v>87.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -3072,37 +3062,37 @@
         <v>46239</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>43</v>
       </c>
       <c r="E53">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F53">
-        <v>5.3800000000000001E-2</v>
+        <v>6.9699999999999998E-2</v>
       </c>
       <c r="G53">
-        <v>0.44030000000000002</v>
+        <v>0.3599</v>
       </c>
       <c r="H53">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="I53">
-        <v>0.4042</v>
+        <v>0.48459999999999998</v>
       </c>
       <c r="J53">
-        <v>0.64590000000000003</v>
+        <v>0.63109999999999999</v>
       </c>
       <c r="K53">
-        <v>5.34</v>
+        <v>4.13</v>
       </c>
       <c r="L53">
-        <v>92</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -3110,37 +3100,37 @@
         <v>46239</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D54">
         <v>44</v>
       </c>
       <c r="E54">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F54">
-        <v>5.4300000000000001E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="G54">
-        <v>0.44390000000000002</v>
+        <v>0.376</v>
       </c>
       <c r="H54">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="I54">
-        <v>0.4214</v>
+        <v>0.4864</v>
       </c>
       <c r="J54">
-        <v>0.6411</v>
+        <v>0.63560000000000005</v>
       </c>
       <c r="K54">
-        <v>4.9400000000000004</v>
+        <v>4.13</v>
       </c>
       <c r="L54">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -3148,37 +3138,37 @@
         <v>46239</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>45</v>
       </c>
       <c r="E55">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F55">
-        <v>5.5199999999999999E-2</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="G55">
-        <v>0.46560000000000001</v>
+        <v>0.37730000000000002</v>
       </c>
       <c r="H55">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="I55">
-        <v>0.41589999999999999</v>
+        <v>0.46689999999999998</v>
       </c>
       <c r="J55">
-        <v>0.65069999999999995</v>
+        <v>0.65780000000000005</v>
       </c>
       <c r="K55">
-        <v>5.12</v>
+        <v>4.62</v>
       </c>
       <c r="L55">
-        <v>90</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -3186,37 +3176,37 @@
         <v>46239</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D56">
         <v>46</v>
       </c>
       <c r="E56">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F56">
-        <v>6.2300000000000001E-2</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="G56">
-        <v>0.44619999999999999</v>
+        <v>0.36130000000000001</v>
       </c>
       <c r="H56">
-        <v>0.56999999999999995</v>
+        <v>0.98</v>
       </c>
       <c r="I56">
-        <v>0.40410000000000001</v>
+        <v>0.4965</v>
       </c>
       <c r="J56">
-        <v>0.65549999999999997</v>
+        <v>0.63560000000000005</v>
       </c>
       <c r="K56">
-        <v>5.42</v>
+        <v>3.97</v>
       </c>
       <c r="L56">
-        <v>88</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -3224,7 +3214,7 @@
         <v>46239</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -3236,25 +3226,25 @@
         <v>0.01</v>
       </c>
       <c r="F57">
-        <v>6.5000000000000002E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="G57">
-        <v>0.45090000000000002</v>
+        <v>0.39450000000000002</v>
       </c>
       <c r="H57">
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="I57">
-        <v>0.39079999999999998</v>
+        <v>0.50719999999999998</v>
       </c>
       <c r="J57">
-        <v>0.65069999999999995</v>
+        <v>0.66990000000000005</v>
       </c>
       <c r="K57">
-        <v>5.69</v>
+        <v>3.65</v>
       </c>
       <c r="L57">
-        <v>85.5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -3262,7 +3252,7 @@
         <v>46239</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -3274,25 +3264,25 @@
         <v>0.01</v>
       </c>
       <c r="F58">
-        <v>5.2999999999999999E-2</v>
+        <v>6.5500000000000003E-2</v>
       </c>
       <c r="G58">
-        <v>0.43759999999999999</v>
+        <v>0.38440000000000002</v>
       </c>
       <c r="H58">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="I58">
-        <v>0.34420000000000001</v>
+        <v>0.53959999999999997</v>
       </c>
       <c r="J58">
-        <v>0.65549999999999997</v>
+        <v>0.68420000000000003</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>3.27</v>
       </c>
       <c r="L58">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -3300,7 +3290,7 @@
         <v>46239</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -3312,25 +3302,25 @@
         <v>0.01</v>
       </c>
       <c r="F59">
-        <v>5.3800000000000001E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="G59">
-        <v>0.44950000000000001</v>
+        <v>0.38150000000000001</v>
       </c>
       <c r="H59">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="I59">
-        <v>0.37290000000000001</v>
+        <v>0.50180000000000002</v>
       </c>
       <c r="J59">
-        <v>0.64590000000000003</v>
+        <v>0.66990000000000005</v>
       </c>
       <c r="K59">
-        <v>6.09</v>
+        <v>3.73</v>
       </c>
       <c r="L59">
-        <v>87</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -3338,7 +3328,7 @@
         <v>46239</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
@@ -3350,25 +3340,25 @@
         <v>0.01</v>
       </c>
       <c r="F60">
-        <v>5.7200000000000001E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="G60">
-        <v>0.45529999999999998</v>
+        <v>0.37419999999999998</v>
       </c>
       <c r="H60">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="I60">
-        <v>0.40429999999999999</v>
+        <v>0.52510000000000001</v>
       </c>
       <c r="J60">
-        <v>0.63639999999999997</v>
+        <v>0.65069999999999995</v>
       </c>
       <c r="K60">
-        <v>5.26</v>
+        <v>3.3</v>
       </c>
       <c r="L60">
-        <v>86</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -3376,7 +3366,7 @@
         <v>46239</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -3388,25 +3378,25 @@
         <v>0.01</v>
       </c>
       <c r="F61">
-        <v>5.0200000000000002E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G61">
-        <v>0.45090000000000002</v>
+        <v>0.34489999999999998</v>
       </c>
       <c r="H61">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="I61">
-        <v>0.41560000000000002</v>
+        <v>0.52939999999999998</v>
       </c>
       <c r="J61">
-        <v>0.63639999999999997</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="K61">
-        <v>5.0199999999999996</v>
+        <v>3.22</v>
       </c>
       <c r="L61">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">

--- a/results/master_row_threshold_results.xlsx
+++ b/results/master_row_threshold_results.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\이데아\ML_HDD2\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\projects\26_2_COIN\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFEEF89-6020-45EF-B57F-36D2DF33F8A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B018ED-F75B-4B8E-BB8D-DD30F51C148E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_row_threshold_results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="19">
   <si>
     <t>Timestamp</t>
   </si>
@@ -249,7 +262,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,8 +442,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -545,6 +564,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -674,11 +704,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -746,8 +782,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C158F239-7827-4398-8C04-34D24A94C0F9}" name="표2" displayName="표2" ref="A1:L61" totalsRowShown="0">
   <autoFilter ref="A1:L61" xr:uid="{59785569-C3B6-4769-BEAC-0848E73DB11A}"/>
-  <sortState ref="A2:L61">
-    <sortCondition ref="B1:B61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L61">
+    <sortCondition ref="D1:D61"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{6C99DCA4-7E4F-4594-BCC8-003022FA31AD}" name="Timestamp" dataDxfId="0"/>
@@ -768,9 +804,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -808,7 +844,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -914,7 +950,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,7 +1092,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1064,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
@@ -1081,7 +1117,7 @@
     <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1118,13 +1154,25 @@
       <c r="L1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46239</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -1136,104 +1184,140 @@
         <v>0.04</v>
       </c>
       <c r="F2">
-        <v>9.4100000000000003E-2</v>
+        <v>7.9799999999999996E-2</v>
       </c>
       <c r="G2">
-        <v>0.42120000000000002</v>
+        <v>0.48649999999999999</v>
       </c>
       <c r="H2">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0.66669999999999996</v>
+        <v>0.58850000000000002</v>
       </c>
       <c r="J2">
-        <v>0.64200000000000002</v>
+        <v>0.75929999999999997</v>
       </c>
       <c r="K2">
-        <v>5.32</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="L2">
-        <v>204.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F3">
-        <v>8.4400000000000003E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="G3">
-        <v>0.42459999999999998</v>
+        <v>0.43759999999999999</v>
       </c>
       <c r="H3">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="I3">
-        <v>0.65429999999999999</v>
+        <v>0.69179999999999997</v>
       </c>
       <c r="J3">
-        <v>0.65429999999999999</v>
+        <v>0.62350000000000005</v>
       </c>
       <c r="K3">
-        <v>5.73</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="L3">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46239</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0.04</v>
       </c>
       <c r="F4">
-        <v>8.2400000000000001E-2</v>
+        <v>9.0399999999999994E-2</v>
       </c>
       <c r="G4">
-        <v>0.37459999999999999</v>
+        <v>0.36449999999999999</v>
       </c>
       <c r="H4">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="I4">
-        <v>0.67810000000000004</v>
+        <v>0.61329999999999996</v>
       </c>
       <c r="J4">
-        <v>0.61109999999999998</v>
+        <v>0.68520000000000003</v>
       </c>
       <c r="K4">
-        <v>4.8099999999999996</v>
+        <v>7.16</v>
       </c>
       <c r="L4">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46239</v>
       </c>
@@ -1244,77 +1328,101 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>0.04</v>
       </c>
       <c r="F5">
-        <v>9.0800000000000006E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="G5">
-        <v>0.41570000000000001</v>
+        <v>0.42120000000000002</v>
       </c>
       <c r="H5">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="I5">
-        <v>0.61619999999999997</v>
+        <v>0.66669999999999996</v>
       </c>
       <c r="J5">
-        <v>0.70369999999999999</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="K5">
-        <v>7.27</v>
+        <v>5.32</v>
       </c>
       <c r="L5">
-        <v>206.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>204.5</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46239</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F6">
-        <v>8.2799999999999999E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="G6">
-        <v>0.37609999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="H6">
-        <v>0.74</v>
+        <v>0.94</v>
       </c>
       <c r="I6">
-        <v>0.64849999999999997</v>
+        <v>0.50170000000000003</v>
       </c>
       <c r="J6">
-        <v>0.66049999999999998</v>
+        <v>0.64</v>
       </c>
       <c r="K6">
-        <v>5.94</v>
+        <v>3.91</v>
       </c>
       <c r="L6">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>30.5</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46239</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -1326,66 +1434,90 @@
         <v>0.02</v>
       </c>
       <c r="F7">
-        <v>7.1800000000000003E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
       <c r="G7">
-        <v>0.39</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="H7">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="I7">
-        <v>0.40770000000000001</v>
+        <v>0.45019999999999999</v>
       </c>
       <c r="J7">
-        <v>0.65780000000000005</v>
+        <v>0.62219999999999998</v>
       </c>
       <c r="K7">
-        <v>5.88</v>
+        <v>4.68</v>
       </c>
       <c r="L7">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>37.5</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46239</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>0.02</v>
       </c>
       <c r="F8">
-        <v>7.4300000000000005E-2</v>
+        <v>7.7299999999999994E-2</v>
       </c>
       <c r="G8">
-        <v>0.36870000000000003</v>
+        <v>0.34510000000000002</v>
       </c>
       <c r="H8">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="I8">
-        <v>0.40500000000000003</v>
+        <v>0.55649999999999999</v>
       </c>
       <c r="J8">
-        <v>0.65329999999999999</v>
+        <v>0.61329999999999996</v>
       </c>
       <c r="K8">
-        <v>5.91</v>
+        <v>3.01</v>
       </c>
       <c r="L8">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>31.5</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46239</v>
       </c>
@@ -1396,115 +1528,151 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>0.02</v>
       </c>
       <c r="F9">
-        <v>7.7399999999999997E-2</v>
+        <v>7.1800000000000003E-2</v>
       </c>
       <c r="G9">
-        <v>0.38779999999999998</v>
+        <v>0.39</v>
       </c>
       <c r="H9">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="I9">
-        <v>0.40600000000000003</v>
+        <v>0.40770000000000001</v>
       </c>
       <c r="J9">
-        <v>0.66220000000000001</v>
+        <v>0.65780000000000005</v>
       </c>
       <c r="K9">
-        <v>5.96</v>
+        <v>5.88</v>
       </c>
       <c r="L9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P9" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46239</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E10">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F10">
-        <v>8.2500000000000004E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="G10">
-        <v>0.36780000000000002</v>
+        <v>0.39450000000000002</v>
       </c>
       <c r="H10">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="I10">
-        <v>0.4269</v>
+        <v>0.50719999999999998</v>
       </c>
       <c r="J10">
-        <v>0.66220000000000001</v>
+        <v>0.66990000000000005</v>
       </c>
       <c r="K10">
-        <v>5.47</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
+        <v>71</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="Q10" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46239</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E11">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F11">
-        <v>6.7299999999999999E-2</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="G11">
-        <v>0.37190000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="H11">
-        <v>0.97</v>
+        <v>0.64</v>
       </c>
       <c r="I11">
-        <v>0.37909999999999999</v>
+        <v>0.42009999999999997</v>
       </c>
       <c r="J11">
-        <v>0.66220000000000001</v>
+        <v>0.6411</v>
       </c>
       <c r="K11">
-        <v>6.67</v>
+        <v>4.96</v>
       </c>
       <c r="L11">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>87.5</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46239</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -1516,28 +1684,40 @@
         <v>0.01</v>
       </c>
       <c r="F12">
-        <v>6.5000000000000002E-2</v>
+        <v>0.1517</v>
       </c>
       <c r="G12">
-        <v>0.45090000000000002</v>
+        <v>0.22489999999999999</v>
       </c>
       <c r="H12">
-        <v>0.55000000000000004</v>
+        <v>0.11</v>
       </c>
       <c r="I12">
-        <v>0.39079999999999998</v>
+        <v>0.68910000000000005</v>
       </c>
       <c r="J12">
-        <v>0.65069999999999995</v>
+        <v>0.39229999999999998</v>
       </c>
       <c r="K12">
-        <v>5.69</v>
+        <v>0.99</v>
       </c>
       <c r="L12">
-        <v>85.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46239</v>
       </c>
@@ -1548,145 +1728,145 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>0.01</v>
       </c>
       <c r="F13">
-        <v>5.2999999999999999E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="G13">
-        <v>0.43759999999999999</v>
+        <v>0.45090000000000002</v>
       </c>
       <c r="H13">
-        <v>0.67</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I13">
-        <v>0.34420000000000001</v>
+        <v>0.39079999999999998</v>
       </c>
       <c r="J13">
-        <v>0.65549999999999997</v>
+        <v>0.65069999999999995</v>
       </c>
       <c r="K13">
+        <v>5.69</v>
+      </c>
+      <c r="L13">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>43</v>
+      </c>
+      <c r="E14">
+        <v>0.04</v>
+      </c>
+      <c r="F14">
+        <v>7.6499999999999999E-2</v>
+      </c>
+      <c r="G14">
+        <v>0.44940000000000002</v>
+      </c>
+      <c r="H14">
+        <v>0.97</v>
+      </c>
+      <c r="I14">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="J14">
+        <v>0.74070000000000003</v>
+      </c>
+      <c r="K14">
+        <v>7.88</v>
+      </c>
+      <c r="L14">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>43</v>
+      </c>
+      <c r="E15">
+        <v>0.04</v>
+      </c>
+      <c r="F15">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="G15">
+        <v>0.39229999999999998</v>
+      </c>
+      <c r="H15">
+        <v>0.95</v>
+      </c>
+      <c r="I15">
+        <v>0.67910000000000004</v>
+      </c>
+      <c r="J15">
+        <v>0.56169999999999998</v>
+      </c>
+      <c r="K15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L15">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="L13">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>46239</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <v>44</v>
-      </c>
-      <c r="E14">
-        <v>0.01</v>
-      </c>
-      <c r="F14">
-        <v>5.3800000000000001E-2</v>
-      </c>
-      <c r="G14">
-        <v>0.44950000000000001</v>
-      </c>
-      <c r="H14">
-        <v>0.68</v>
-      </c>
-      <c r="I14">
-        <v>0.37290000000000001</v>
-      </c>
-      <c r="J14">
-        <v>0.64590000000000003</v>
-      </c>
-      <c r="K14">
-        <v>6.09</v>
-      </c>
-      <c r="L14">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>46239</v>
-      </c>
-      <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15">
-        <v>45</v>
-      </c>
-      <c r="E15">
-        <v>0.01</v>
-      </c>
-      <c r="F15">
-        <v>5.7200000000000001E-2</v>
-      </c>
-      <c r="G15">
-        <v>0.45529999999999998</v>
-      </c>
-      <c r="H15">
-        <v>0.64</v>
-      </c>
-      <c r="I15">
-        <v>0.40429999999999999</v>
-      </c>
-      <c r="J15">
-        <v>0.63639999999999997</v>
-      </c>
-      <c r="K15">
-        <v>5.26</v>
-      </c>
-      <c r="L15">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>46239</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E16">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F16">
-        <v>5.0200000000000002E-2</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G16">
-        <v>0.45090000000000002</v>
+        <v>0.3765</v>
       </c>
       <c r="H16">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="I16">
-        <v>0.41560000000000002</v>
+        <v>0.66469999999999996</v>
       </c>
       <c r="J16">
-        <v>0.63639999999999997</v>
+        <v>0.68520000000000003</v>
       </c>
       <c r="K16">
-        <v>5.0199999999999996</v>
+        <v>5.73</v>
       </c>
       <c r="L16">
-        <v>83</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1694,37 +1874,37 @@
         <v>46239</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17">
         <v>0.04</v>
       </c>
       <c r="F17">
-        <v>9.0399999999999994E-2</v>
+        <v>8.4400000000000003E-2</v>
       </c>
       <c r="G17">
-        <v>0.36449999999999999</v>
+        <v>0.42459999999999998</v>
       </c>
       <c r="H17">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="I17">
-        <v>0.61329999999999996</v>
+        <v>0.65429999999999999</v>
       </c>
       <c r="J17">
-        <v>0.68520000000000003</v>
+        <v>0.65429999999999999</v>
       </c>
       <c r="K17">
-        <v>7.16</v>
+        <v>5.73</v>
       </c>
       <c r="L17">
-        <v>168</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1732,10 +1912,10 @@
         <v>46239</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>43</v>
@@ -1744,25 +1924,25 @@
         <v>0.02</v>
       </c>
       <c r="F18">
-        <v>7.9699999999999993E-2</v>
+        <v>6.9699999999999998E-2</v>
       </c>
       <c r="G18">
-        <v>0.3765</v>
+        <v>0.3599</v>
       </c>
       <c r="H18">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="I18">
-        <v>0.66469999999999996</v>
+        <v>0.48459999999999998</v>
       </c>
       <c r="J18">
-        <v>0.68520000000000003</v>
+        <v>0.63109999999999999</v>
       </c>
       <c r="K18">
-        <v>5.73</v>
+        <v>4.13</v>
       </c>
       <c r="L18">
-        <v>169</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1770,37 +1950,37 @@
         <v>46239</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F19">
-        <v>9.4E-2</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="G19">
-        <v>0.36699999999999999</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="H19">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="I19">
-        <v>0.62570000000000003</v>
+        <v>0.39510000000000001</v>
       </c>
       <c r="J19">
-        <v>0.69140000000000001</v>
+        <v>0.64439999999999997</v>
       </c>
       <c r="K19">
-        <v>6.86</v>
+        <v>6.07</v>
       </c>
       <c r="L19">
-        <v>167.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1811,34 +1991,34 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E20">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F20">
-        <v>0.1061</v>
+        <v>8.1900000000000001E-2</v>
       </c>
       <c r="G20">
-        <v>0.24079999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="H20">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="I20">
-        <v>0.63160000000000005</v>
+        <v>0.53659999999999997</v>
       </c>
       <c r="J20">
-        <v>0.51849999999999996</v>
+        <v>0.5867</v>
       </c>
       <c r="K20">
-        <v>5.0199999999999996</v>
+        <v>3.12</v>
       </c>
       <c r="L20">
-        <v>134</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1846,37 +2026,37 @@
         <v>46239</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F21">
-        <v>7.0900000000000005E-2</v>
+        <v>7.4300000000000005E-2</v>
       </c>
       <c r="G21">
-        <v>0.4254</v>
+        <v>0.36870000000000003</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="I21">
-        <v>0.60199999999999998</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="J21">
-        <v>0.72840000000000005</v>
+        <v>0.65329999999999999</v>
       </c>
       <c r="K21">
-        <v>7.98</v>
+        <v>5.91</v>
       </c>
       <c r="L21">
-        <v>220.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1884,37 +2064,37 @@
         <v>46239</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D22">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F22">
-        <v>7.7299999999999994E-2</v>
+        <v>6.5500000000000003E-2</v>
       </c>
       <c r="G22">
-        <v>0.34510000000000002</v>
+        <v>0.38440000000000002</v>
       </c>
       <c r="H22">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="I22">
-        <v>0.55649999999999999</v>
+        <v>0.53959999999999997</v>
       </c>
       <c r="J22">
-        <v>0.61329999999999996</v>
+        <v>0.68420000000000003</v>
       </c>
       <c r="K22">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="L22">
-        <v>31.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1922,37 +2102,37 @@
         <v>46239</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D23">
         <v>43</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F23">
-        <v>8.1900000000000001E-2</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="G23">
-        <v>0.34320000000000001</v>
+        <v>0.44030000000000002</v>
       </c>
       <c r="H23">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="I23">
-        <v>0.53659999999999997</v>
+        <v>0.4042</v>
       </c>
       <c r="J23">
-        <v>0.5867</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="K23">
-        <v>3.12</v>
+        <v>5.34</v>
       </c>
       <c r="L23">
-        <v>34</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1963,34 +2143,34 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D24">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F24">
-        <v>7.7100000000000002E-2</v>
+        <v>0.1615</v>
       </c>
       <c r="G24">
-        <v>0.35360000000000003</v>
+        <v>0.25690000000000002</v>
       </c>
       <c r="H24">
-        <v>0.8</v>
+        <v>0.11</v>
       </c>
       <c r="I24">
-        <v>0.50939999999999996</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J24">
-        <v>0.6</v>
+        <v>0.46410000000000001</v>
       </c>
       <c r="K24">
-        <v>3.56</v>
+        <v>1.05</v>
       </c>
       <c r="L24">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1998,37 +2178,37 @@
         <v>46239</v>
       </c>
       <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>43</v>
+      </c>
+      <c r="E25">
+        <v>0.01</v>
+      </c>
+      <c r="F25">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G25">
+        <v>0.43759999999999999</v>
+      </c>
+      <c r="H25">
+        <v>0.67</v>
+      </c>
+      <c r="I25">
+        <v>0.34420000000000001</v>
+      </c>
+      <c r="J25">
+        <v>0.65549999999999997</v>
+      </c>
+      <c r="K25">
         <v>7</v>
       </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25">
-        <v>45</v>
-      </c>
-      <c r="E25">
-        <v>0.02</v>
-      </c>
-      <c r="F25">
-        <v>7.8799999999999995E-2</v>
-      </c>
-      <c r="G25">
-        <v>0.33350000000000002</v>
-      </c>
-      <c r="H25">
-        <v>0.73</v>
-      </c>
-      <c r="I25">
-        <v>0.54879999999999995</v>
-      </c>
-      <c r="J25">
-        <v>0.6</v>
-      </c>
-      <c r="K25">
-        <v>3.04</v>
-      </c>
       <c r="L25">
-        <v>30</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -2036,37 +2216,37 @@
         <v>46239</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E26">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F26">
-        <v>8.1000000000000003E-2</v>
+        <v>9.3700000000000006E-2</v>
       </c>
       <c r="G26">
-        <v>0.32279999999999998</v>
+        <v>0.39910000000000001</v>
       </c>
       <c r="H26">
         <v>0.69</v>
       </c>
       <c r="I26">
-        <v>0.55600000000000005</v>
+        <v>0.63129999999999997</v>
       </c>
       <c r="J26">
-        <v>0.59560000000000002</v>
+        <v>0.69750000000000001</v>
       </c>
       <c r="K26">
-        <v>2.93</v>
+        <v>6.76</v>
       </c>
       <c r="L26">
-        <v>26</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -2074,37 +2254,37 @@
         <v>46239</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E27">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F27">
-        <v>0.1517</v>
+        <v>7.8399999999999997E-2</v>
       </c>
       <c r="G27">
-        <v>0.22489999999999999</v>
+        <v>0.3795</v>
       </c>
       <c r="H27">
-        <v>0.11</v>
+        <v>0.8</v>
       </c>
       <c r="I27">
-        <v>0.68910000000000005</v>
+        <v>0.66449999999999998</v>
       </c>
       <c r="J27">
-        <v>0.39229999999999998</v>
+        <v>0.63580000000000003</v>
       </c>
       <c r="K27">
-        <v>0.99</v>
+        <v>5.32</v>
       </c>
       <c r="L27">
-        <v>65</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -2115,34 +2295,34 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F28">
-        <v>0.1615</v>
+        <v>9.4E-2</v>
       </c>
       <c r="G28">
-        <v>0.25690000000000002</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="H28">
-        <v>0.11</v>
+        <v>0.63</v>
       </c>
       <c r="I28">
-        <v>0.71319999999999995</v>
+        <v>0.62570000000000003</v>
       </c>
       <c r="J28">
-        <v>0.46410000000000001</v>
+        <v>0.69140000000000001</v>
       </c>
       <c r="K28">
-        <v>1.05</v>
+        <v>6.86</v>
       </c>
       <c r="L28">
-        <v>51</v>
+        <v>167.5</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -2150,37 +2330,37 @@
         <v>46239</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29">
         <v>44</v>
       </c>
       <c r="E29">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F29">
-        <v>0.1615</v>
+        <v>8.2400000000000001E-2</v>
       </c>
       <c r="G29">
-        <v>0.25359999999999999</v>
+        <v>0.37459999999999999</v>
       </c>
       <c r="H29">
-        <v>0.11</v>
+        <v>0.75</v>
       </c>
       <c r="I29">
-        <v>0.71109999999999995</v>
+        <v>0.67810000000000004</v>
       </c>
       <c r="J29">
-        <v>0.45929999999999999</v>
+        <v>0.61109999999999998</v>
       </c>
       <c r="K29">
-        <v>1.05</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="L29">
-        <v>47</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -2188,37 +2368,37 @@
         <v>46239</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F30">
-        <v>0.16300000000000001</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="G30">
-        <v>0.26069999999999999</v>
+        <v>0.376</v>
       </c>
       <c r="H30">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="I30">
-        <v>0.71319999999999995</v>
+        <v>0.4864</v>
       </c>
       <c r="J30">
-        <v>0.46410000000000001</v>
+        <v>0.63560000000000005</v>
       </c>
       <c r="K30">
-        <v>1.05</v>
+        <v>4.13</v>
       </c>
       <c r="L30">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -2226,37 +2406,37 @@
         <v>46239</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D31">
+        <v>44</v>
+      </c>
+      <c r="E31">
+        <v>0.02</v>
+      </c>
+      <c r="F31">
+        <v>6.2799999999999995E-2</v>
+      </c>
+      <c r="G31">
+        <v>0.37890000000000001</v>
+      </c>
+      <c r="H31">
+        <v>1.06</v>
+      </c>
+      <c r="I31">
+        <v>0.39779999999999999</v>
+      </c>
+      <c r="J31">
+        <v>0.64890000000000003</v>
+      </c>
+      <c r="K31">
+        <v>6.04</v>
+      </c>
+      <c r="L31">
         <v>46</v>
-      </c>
-      <c r="E31">
-        <v>0.01</v>
-      </c>
-      <c r="F31">
-        <v>0.16300000000000001</v>
-      </c>
-      <c r="G31">
-        <v>0.26069999999999999</v>
-      </c>
-      <c r="H31">
-        <v>0.11</v>
-      </c>
-      <c r="I31">
-        <v>0.71319999999999995</v>
-      </c>
-      <c r="J31">
-        <v>0.46410000000000001</v>
-      </c>
-      <c r="K31">
-        <v>1.05</v>
-      </c>
-      <c r="L31">
-        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -2264,37 +2444,37 @@
         <v>46239</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D32">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E32">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F32">
-        <v>7.3999999999999996E-2</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="G32">
-        <v>0.43759999999999999</v>
+        <v>0.35360000000000003</v>
       </c>
       <c r="H32">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="I32">
-        <v>0.69179999999999997</v>
+        <v>0.50939999999999996</v>
       </c>
       <c r="J32">
-        <v>0.62350000000000005</v>
+        <v>0.6</v>
       </c>
       <c r="K32">
-        <v>4.6100000000000003</v>
+        <v>3.56</v>
       </c>
       <c r="L32">
-        <v>174</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -2302,37 +2482,37 @@
         <v>46239</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D33">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E33">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F33">
-        <v>6.9000000000000006E-2</v>
+        <v>7.7399999999999997E-2</v>
       </c>
       <c r="G33">
-        <v>0.39229999999999998</v>
+        <v>0.38779999999999998</v>
       </c>
       <c r="H33">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="I33">
-        <v>0.67910000000000004</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="J33">
-        <v>0.56169999999999998</v>
+        <v>0.66220000000000001</v>
       </c>
       <c r="K33">
-        <v>4.4000000000000004</v>
+        <v>5.96</v>
       </c>
       <c r="L33">
-        <v>158</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -2340,37 +2520,37 @@
         <v>46239</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34">
         <v>44</v>
       </c>
       <c r="E34">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F34">
-        <v>7.8399999999999997E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="G34">
-        <v>0.3795</v>
+        <v>0.38150000000000001</v>
       </c>
       <c r="H34">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="I34">
-        <v>0.66449999999999998</v>
+        <v>0.50180000000000002</v>
       </c>
       <c r="J34">
-        <v>0.63580000000000003</v>
+        <v>0.66990000000000005</v>
       </c>
       <c r="K34">
-        <v>5.32</v>
+        <v>3.73</v>
       </c>
       <c r="L34">
-        <v>174</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -2381,34 +2561,34 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F35">
-        <v>7.1900000000000006E-2</v>
+        <v>5.4300000000000001E-2</v>
       </c>
       <c r="G35">
-        <v>0.3866</v>
+        <v>0.44390000000000002</v>
       </c>
       <c r="H35">
-        <v>0.89</v>
+        <v>0.66</v>
       </c>
       <c r="I35">
-        <v>0.65849999999999997</v>
+        <v>0.4214</v>
       </c>
       <c r="J35">
-        <v>0.66669999999999996</v>
+        <v>0.6411</v>
       </c>
       <c r="K35">
-        <v>5.73</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="L35">
-        <v>186.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -2416,37 +2596,37 @@
         <v>46239</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F36">
-        <v>8.0600000000000005E-2</v>
+        <v>0.1615</v>
       </c>
       <c r="G36">
-        <v>0.40639999999999998</v>
+        <v>0.25359999999999999</v>
       </c>
       <c r="H36">
-        <v>0.83</v>
+        <v>0.11</v>
       </c>
       <c r="I36">
-        <v>0.69569999999999999</v>
+        <v>0.71109999999999995</v>
       </c>
       <c r="J36">
-        <v>0.59260000000000002</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="K36">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="L36">
-        <v>168</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -2454,37 +2634,37 @@
         <v>46239</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E37">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F37">
-        <v>7.5700000000000003E-2</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="G37">
-        <v>0.36599999999999999</v>
+        <v>0.44950000000000001</v>
       </c>
       <c r="H37">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="I37">
-        <v>0.45019999999999999</v>
+        <v>0.37290000000000001</v>
       </c>
       <c r="J37">
-        <v>0.62219999999999998</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="K37">
-        <v>4.68</v>
+        <v>6.09</v>
       </c>
       <c r="L37">
-        <v>37.5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2492,37 +2672,37 @@
         <v>46239</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E38">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F38">
-        <v>6.9500000000000006E-2</v>
+        <v>8.0799999999999997E-2</v>
       </c>
       <c r="G38">
-        <v>0.35399999999999998</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="H38">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="I38">
-        <v>0.39510000000000001</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="J38">
-        <v>0.64439999999999997</v>
+        <v>0.73460000000000003</v>
       </c>
       <c r="K38">
-        <v>6.07</v>
+        <v>8.09</v>
       </c>
       <c r="L38">
-        <v>47</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2533,34 +2713,34 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E39">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F39">
-        <v>6.2799999999999995E-2</v>
+        <v>7.1900000000000006E-2</v>
       </c>
       <c r="G39">
-        <v>0.37890000000000001</v>
+        <v>0.3866</v>
       </c>
       <c r="H39">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="I39">
-        <v>0.39779999999999999</v>
+        <v>0.65849999999999997</v>
       </c>
       <c r="J39">
-        <v>0.64890000000000003</v>
+        <v>0.66669999999999996</v>
       </c>
       <c r="K39">
-        <v>6.04</v>
+        <v>5.73</v>
       </c>
       <c r="L39">
-        <v>46</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2568,37 +2748,37 @@
         <v>46239</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D40">
         <v>45</v>
       </c>
       <c r="E40">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F40">
-        <v>7.0300000000000001E-2</v>
+        <v>0.1061</v>
       </c>
       <c r="G40">
-        <v>0.38640000000000002</v>
+        <v>0.24079999999999999</v>
       </c>
       <c r="H40">
-        <v>0.96</v>
+        <v>0.36</v>
       </c>
       <c r="I40">
-        <v>0.4103</v>
+        <v>0.63160000000000005</v>
       </c>
       <c r="J40">
-        <v>0.64</v>
+        <v>0.51849999999999996</v>
       </c>
       <c r="K40">
-        <v>5.66</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="L40">
-        <v>48.5</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2606,37 +2786,37 @@
         <v>46239</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D41">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F41">
-        <v>6.6299999999999998E-2</v>
+        <v>9.0800000000000006E-2</v>
       </c>
       <c r="G41">
-        <v>0.3821</v>
+        <v>0.41570000000000001</v>
       </c>
       <c r="H41">
-        <v>1.01</v>
+        <v>0.74</v>
       </c>
       <c r="I41">
-        <v>0.39889999999999998</v>
+        <v>0.61619999999999997</v>
       </c>
       <c r="J41">
-        <v>0.64890000000000003</v>
+        <v>0.70369999999999999</v>
       </c>
       <c r="K41">
-        <v>6.02</v>
+        <v>7.27</v>
       </c>
       <c r="L41">
-        <v>49</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2644,37 +2824,37 @@
         <v>46239</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D42">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E42">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F42">
-        <v>5.5800000000000002E-2</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="G42">
-        <v>0.44</v>
+        <v>0.37730000000000002</v>
       </c>
       <c r="H42">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="I42">
-        <v>0.42009999999999997</v>
+        <v>0.46689999999999998</v>
       </c>
       <c r="J42">
-        <v>0.6411</v>
+        <v>0.65780000000000005</v>
       </c>
       <c r="K42">
-        <v>4.96</v>
+        <v>4.62</v>
       </c>
       <c r="L42">
-        <v>87.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2685,34 +2865,34 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E43">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F43">
-        <v>5.3800000000000001E-2</v>
+        <v>7.0300000000000001E-2</v>
       </c>
       <c r="G43">
-        <v>0.44030000000000002</v>
+        <v>0.38640000000000002</v>
       </c>
       <c r="H43">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="I43">
-        <v>0.4042</v>
+        <v>0.4103</v>
       </c>
       <c r="J43">
-        <v>0.64590000000000003</v>
+        <v>0.64</v>
       </c>
       <c r="K43">
-        <v>5.34</v>
+        <v>5.66</v>
       </c>
       <c r="L43">
-        <v>92</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2720,37 +2900,37 @@
         <v>46239</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D44">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E44">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F44">
-        <v>5.4300000000000001E-2</v>
+        <v>7.8799999999999995E-2</v>
       </c>
       <c r="G44">
-        <v>0.44390000000000002</v>
+        <v>0.33350000000000002</v>
       </c>
       <c r="H44">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="I44">
-        <v>0.4214</v>
+        <v>0.54879999999999995</v>
       </c>
       <c r="J44">
-        <v>0.6411</v>
+        <v>0.6</v>
       </c>
       <c r="K44">
-        <v>4.9400000000000004</v>
+        <v>3.04</v>
       </c>
       <c r="L44">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2758,37 +2938,37 @@
         <v>46239</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D45">
         <v>45</v>
       </c>
       <c r="E45">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F45">
-        <v>5.5199999999999999E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="G45">
-        <v>0.46560000000000001</v>
+        <v>0.36780000000000002</v>
       </c>
       <c r="H45">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="I45">
-        <v>0.41589999999999999</v>
+        <v>0.4269</v>
       </c>
       <c r="J45">
-        <v>0.65069999999999995</v>
+        <v>0.66220000000000001</v>
       </c>
       <c r="K45">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="L45">
-        <v>90</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2796,37 +2976,37 @@
         <v>46239</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
       </c>
       <c r="D46">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46">
         <v>0.01</v>
       </c>
       <c r="F46">
-        <v>6.2300000000000001E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="G46">
-        <v>0.44619999999999999</v>
+        <v>0.37419999999999998</v>
       </c>
       <c r="H46">
-        <v>0.56999999999999995</v>
+        <v>0.46</v>
       </c>
       <c r="I46">
-        <v>0.40410000000000001</v>
+        <v>0.52510000000000001</v>
       </c>
       <c r="J46">
-        <v>0.65549999999999997</v>
+        <v>0.65069999999999995</v>
       </c>
       <c r="K46">
-        <v>5.42</v>
+        <v>3.3</v>
       </c>
       <c r="L46">
-        <v>88</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2834,37 +3014,37 @@
         <v>46239</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E47">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F47">
-        <v>7.9799999999999996E-2</v>
+        <v>5.5199999999999999E-2</v>
       </c>
       <c r="G47">
-        <v>0.48649999999999999</v>
+        <v>0.46560000000000001</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="I47">
-        <v>0.58850000000000002</v>
+        <v>0.41589999999999999</v>
       </c>
       <c r="J47">
-        <v>0.75929999999999997</v>
+        <v>0.65069999999999995</v>
       </c>
       <c r="K47">
-        <v>8.8000000000000007</v>
+        <v>5.12</v>
       </c>
       <c r="L47">
-        <v>223</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2872,37 +3052,37 @@
         <v>46239</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E48">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F48">
-        <v>7.6499999999999999E-2</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="G48">
-        <v>0.44940000000000002</v>
+        <v>0.26069999999999999</v>
       </c>
       <c r="H48">
-        <v>0.97</v>
+        <v>0.11</v>
       </c>
       <c r="I48">
-        <v>0.60909999999999997</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J48">
-        <v>0.74070000000000003</v>
+        <v>0.46410000000000001</v>
       </c>
       <c r="K48">
-        <v>7.88</v>
+        <v>1.05</v>
       </c>
       <c r="L48">
-        <v>243</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2910,37 +3090,37 @@
         <v>46239</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D49">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F49">
-        <v>9.3700000000000006E-2</v>
+        <v>5.7200000000000001E-2</v>
       </c>
       <c r="G49">
-        <v>0.39910000000000001</v>
+        <v>0.45529999999999998</v>
       </c>
       <c r="H49">
-        <v>0.69</v>
+        <v>0.64</v>
       </c>
       <c r="I49">
-        <v>0.63129999999999997</v>
+        <v>0.40429999999999999</v>
       </c>
       <c r="J49">
-        <v>0.69750000000000001</v>
+        <v>0.63639999999999997</v>
       </c>
       <c r="K49">
-        <v>6.76</v>
+        <v>5.26</v>
       </c>
       <c r="L49">
-        <v>184</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2954,31 +3134,31 @@
         <v>12</v>
       </c>
       <c r="D50">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50">
         <v>0.04</v>
       </c>
       <c r="F50">
-        <v>8.0799999999999997E-2</v>
+        <v>7.7600000000000002E-2</v>
       </c>
       <c r="G50">
-        <v>0.45929999999999999</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="H50">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="I50">
         <v>0.60099999999999998</v>
       </c>
       <c r="J50">
-        <v>0.73460000000000003</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="K50">
-        <v>8.09</v>
+        <v>7.88</v>
       </c>
       <c r="L50">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2986,7 +3166,7 @@
         <v>46239</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -2998,25 +3178,25 @@
         <v>0.04</v>
       </c>
       <c r="F51">
-        <v>7.7600000000000002E-2</v>
+        <v>8.0600000000000005E-2</v>
       </c>
       <c r="G51">
-        <v>0.45700000000000002</v>
+        <v>0.40639999999999998</v>
       </c>
       <c r="H51">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="I51">
-        <v>0.60099999999999998</v>
+        <v>0.69569999999999999</v>
       </c>
       <c r="J51">
-        <v>0.71599999999999997</v>
+        <v>0.59260000000000002</v>
       </c>
       <c r="K51">
-        <v>7.88</v>
+        <v>4.3</v>
       </c>
       <c r="L51">
-        <v>246</v>
+        <v>168</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -3024,37 +3204,37 @@
         <v>46239</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D52">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E52">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F52">
-        <v>6.7199999999999996E-2</v>
+        <v>7.0900000000000005E-2</v>
       </c>
       <c r="G52">
-        <v>0.36</v>
+        <v>0.4254</v>
       </c>
       <c r="H52">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0.50170000000000003</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="J52">
-        <v>0.64</v>
+        <v>0.72840000000000005</v>
       </c>
       <c r="K52">
-        <v>3.91</v>
+        <v>7.98</v>
       </c>
       <c r="L52">
-        <v>30.5</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -3062,37 +3242,37 @@
         <v>46239</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D53">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E53">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F53">
-        <v>6.9699999999999998E-2</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="G53">
-        <v>0.3599</v>
+        <v>0.37609999999999999</v>
       </c>
       <c r="H53">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="I53">
-        <v>0.48459999999999998</v>
+        <v>0.64849999999999997</v>
       </c>
       <c r="J53">
-        <v>0.63109999999999999</v>
+        <v>0.66049999999999998</v>
       </c>
       <c r="K53">
-        <v>4.13</v>
+        <v>5.94</v>
       </c>
       <c r="L53">
-        <v>39</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -3106,31 +3286,31 @@
         <v>8</v>
       </c>
       <c r="D54">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E54">
         <v>0.02</v>
       </c>
       <c r="F54">
-        <v>6.7400000000000002E-2</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="G54">
-        <v>0.376</v>
+        <v>0.36130000000000001</v>
       </c>
       <c r="H54">
         <v>0.98</v>
       </c>
       <c r="I54">
-        <v>0.4864</v>
+        <v>0.4965</v>
       </c>
       <c r="J54">
         <v>0.63560000000000005</v>
       </c>
       <c r="K54">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="L54">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -3138,37 +3318,37 @@
         <v>46239</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
       </c>
       <c r="D55">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E55">
         <v>0.02</v>
       </c>
       <c r="F55">
-        <v>6.8699999999999997E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="G55">
-        <v>0.37730000000000002</v>
+        <v>0.3821</v>
       </c>
       <c r="H55">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="I55">
-        <v>0.46689999999999998</v>
+        <v>0.39889999999999998</v>
       </c>
       <c r="J55">
-        <v>0.65780000000000005</v>
+        <v>0.64890000000000003</v>
       </c>
       <c r="K55">
-        <v>4.62</v>
+        <v>6.02</v>
       </c>
       <c r="L55">
-        <v>41.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -3176,7 +3356,7 @@
         <v>46239</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
@@ -3188,25 +3368,25 @@
         <v>0.02</v>
       </c>
       <c r="F56">
-        <v>6.4600000000000005E-2</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="G56">
-        <v>0.36130000000000001</v>
+        <v>0.32279999999999998</v>
       </c>
       <c r="H56">
-        <v>0.98</v>
+        <v>0.69</v>
       </c>
       <c r="I56">
-        <v>0.4965</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="J56">
-        <v>0.63560000000000005</v>
+        <v>0.59560000000000002</v>
       </c>
       <c r="K56">
-        <v>3.97</v>
+        <v>2.93</v>
       </c>
       <c r="L56">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -3214,37 +3394,37 @@
         <v>46239</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D57">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E57">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F57">
-        <v>6.3500000000000001E-2</v>
+        <v>6.7299999999999999E-2</v>
       </c>
       <c r="G57">
-        <v>0.39450000000000002</v>
+        <v>0.37190000000000001</v>
       </c>
       <c r="H57">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="I57">
-        <v>0.50719999999999998</v>
+        <v>0.37909999999999999</v>
       </c>
       <c r="J57">
-        <v>0.66990000000000005</v>
+        <v>0.66220000000000001</v>
       </c>
       <c r="K57">
-        <v>3.65</v>
+        <v>6.67</v>
       </c>
       <c r="L57">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -3258,31 +3438,31 @@
         <v>13</v>
       </c>
       <c r="D58">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E58">
         <v>0.01</v>
       </c>
       <c r="F58">
-        <v>6.5500000000000003E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G58">
-        <v>0.38440000000000002</v>
+        <v>0.34489999999999998</v>
       </c>
       <c r="H58">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="I58">
-        <v>0.53959999999999997</v>
+        <v>0.52939999999999998</v>
       </c>
       <c r="J58">
-        <v>0.68420000000000003</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="K58">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="L58">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -3290,37 +3470,37 @@
         <v>46239</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
       </c>
       <c r="D59">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E59">
         <v>0.01</v>
       </c>
       <c r="F59">
-        <v>6.5699999999999995E-2</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="G59">
-        <v>0.38150000000000001</v>
+        <v>0.44619999999999999</v>
       </c>
       <c r="H59">
-        <v>0.46</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I59">
-        <v>0.50180000000000002</v>
+        <v>0.40410000000000001</v>
       </c>
       <c r="J59">
-        <v>0.66990000000000005</v>
+        <v>0.65549999999999997</v>
       </c>
       <c r="K59">
-        <v>3.73</v>
+        <v>5.42</v>
       </c>
       <c r="L59">
-        <v>72.5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -3328,37 +3508,37 @@
         <v>46239</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E60">
         <v>0.01</v>
       </c>
       <c r="F60">
-        <v>6.4500000000000002E-2</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="G60">
-        <v>0.37419999999999998</v>
+        <v>0.26069999999999999</v>
       </c>
       <c r="H60">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="I60">
-        <v>0.52510000000000001</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J60">
-        <v>0.65069999999999995</v>
+        <v>0.46410000000000001</v>
       </c>
       <c r="K60">
-        <v>3.3</v>
+        <v>1.05</v>
       </c>
       <c r="L60">
-        <v>61.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -3366,7 +3546,7 @@
         <v>46239</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -3378,25 +3558,25 @@
         <v>0.01</v>
       </c>
       <c r="F61">
-        <v>6.9000000000000006E-2</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="G61">
-        <v>0.34489999999999998</v>
+        <v>0.45090000000000002</v>
       </c>
       <c r="H61">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="I61">
-        <v>0.52939999999999998</v>
+        <v>0.41560000000000002</v>
       </c>
       <c r="J61">
-        <v>0.64590000000000003</v>
+        <v>0.63639999999999997</v>
       </c>
       <c r="K61">
-        <v>3.22</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="L61">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
